--- a/gantt_tfm_completo.xlsx
+++ b/gantt_tfm_completo.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/97B404005393A13D/tfm/planify-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA78810-EA29-4848-BD19-BFD7265F6621}"/>
   <bookViews>
-    <workbookView xWindow="6216" yWindow="1692" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama de Gantt" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1 (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="5" r:id="rId2"/>
+    <sheet name="Hoja1 (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId4"/>
+    <sheet name="Hoja2" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Incremento_de_desplazamiento" localSheetId="1">'Hoja1 (2)'!$C$7</definedName>
-    <definedName name="Inicio_del_proyecto" localSheetId="1">'Hoja1 (2)'!$C$6</definedName>
+    <definedName name="Incremento_de_desplazamiento" localSheetId="2">'Hoja1 (2)'!$C$7</definedName>
+    <definedName name="Inicio_del_proyecto" localSheetId="2">'Hoja1 (2)'!$C$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="121">
   <si>
     <t>Descripción del hito</t>
   </si>
@@ -276,6 +278,137 @@
   </si>
   <si>
     <t>semana 3</t>
+  </si>
+  <si>
+    <t>Hores
+est.</t>
+  </si>
+  <si>
+    <t>% Real
+compl.</t>
+  </si>
+  <si>
+    <t>Fase / Tarea</t>
+  </si>
+  <si>
+    <t>Horas est.</t>
+  </si>
+  <si>
+    <t>% Real compl.</t>
+  </si>
+  <si>
+    <t>Riesgos identificados</t>
+  </si>
+  <si>
+    <t>Plan de contingencia</t>
+  </si>
+  <si>
+    <t>1.1 Estudio, análisis y evaluación objetivos</t>
+  </si>
+  <si>
+    <t>Definición de objetivos y alcance</t>
+  </si>
+  <si>
+    <t>Falta de claridad en los objetivos iniciales</t>
+  </si>
+  <si>
+    <t>Revisión con tutor y ajuste del alcance antes de avanzar</t>
+  </si>
+  <si>
+    <t>1.2 Análisis herramientas disponibles y MVP</t>
+  </si>
+  <si>
+    <t>Evaluación de APIs y frameworks</t>
+  </si>
+  <si>
+    <t>Herramientas incompatibles o con licencias restrictivas</t>
+  </si>
+  <si>
+    <t>Sustituir por alternativas open source (aTurnos, PostgreSQL, Angular)</t>
+  </si>
+  <si>
+    <t>2.4 Desarrollo base de datos con PostgreSQL</t>
+  </si>
+  <si>
+    <t>Diseño y conexión con backend</t>
+  </si>
+  <si>
+    <t>Fallos de conexión o pérdida de datos</t>
+  </si>
+  <si>
+    <t>Implementar backups automáticos y pruebas de conexión SSL</t>
+  </si>
+  <si>
+    <t>2.5 Desarrollo backend con Node.js</t>
+  </si>
+  <si>
+    <t>Creación de API REST y autenticación</t>
+  </si>
+  <si>
+    <t>Errores en autenticación o seguridad JWT</t>
+  </si>
+  <si>
+    <t>Añadir tests unitarios y validación de tokens en middleware</t>
+  </si>
+  <si>
+    <t>2.6 Desarrollo frontend con Angular</t>
+  </si>
+  <si>
+    <t>Implementación de vistas y componentes</t>
+  </si>
+  <si>
+    <t>Desajuste visual o errores de compilación</t>
+  </si>
+  <si>
+    <t>Uso de Angular CLI y revisión de estilos globales</t>
+  </si>
+  <si>
+    <t>3.2 Análisis de resultados y corrección errores</t>
+  </si>
+  <si>
+    <t>Depuración y optimización</t>
+  </si>
+  <si>
+    <t>Bugs críticos en producción</t>
+  </si>
+  <si>
+    <t>Activar logs y rollback en Render</t>
+  </si>
+  <si>
+    <t>4.3 Elaboración de la memoria final</t>
+  </si>
+  <si>
+    <t>Redacción y justificación técnica</t>
+  </si>
+  <si>
+    <t>Retrasos por carga de trabajo</t>
+  </si>
+  <si>
+    <t>Planificar sesiones diarias de redacción y revisión con tutor</t>
+  </si>
+  <si>
+    <t>4.5 Preparación defensa TFM</t>
+  </si>
+  <si>
+    <t>Ensayo y presentación</t>
+  </si>
+  <si>
+    <t>Falta de tiempo para preparar defensa</t>
+  </si>
+  <si>
+    <t>Crear guion y practicar con simulación grabada</t>
+  </si>
+  <si>
+    <t>3.5. Despliegue en servidor público</t>
+  </si>
+  <si>
+    <t>3.6. Tests unitarios</t>
+  </si>
+  <si>
+    <t>3.7. Elaboración vídeo MVP</t>
+  </si>
+  <si>
+    <t>Inicio real</t>
   </si>
 </sst>
 </file>
@@ -286,7 +419,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,8 +517,66 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1A5C1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF8B5E00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,6 +721,54 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
+        <bgColor rgb="FF404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF1F6B8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCBC"/>
+        <bgColor rgb="FFF9D5C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+        <bgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFB8D0ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70BF6A"/>
+        <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE066"/>
+        <bgColor rgb="FFFFFF66"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -579,7 +818,7 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,9 +838,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -612,9 +848,6 @@
     <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -750,6 +983,94 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1024,16 +1345,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="19" width="5" customWidth="1"/>
+    <col min="4" max="18" width="5" customWidth="1"/>
+    <col min="19" max="20" width="8" customWidth="1"/>
+    <col min="21" max="21" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1041,93 +1364,105 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65" t="s">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65" t="s">
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-    </row>
-    <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="V1" s="64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+    </row>
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -1142,9 +1477,16 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-    </row>
-    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="66">
+        <v>27</v>
+      </c>
+      <c r="T3" s="72">
+        <v>1</v>
+      </c>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+    </row>
+    <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1152,173 +1494,201 @@
         <v>46071</v>
       </c>
       <c r="C4" s="8">
-        <v>46077</v>
-      </c>
-      <c r="D4" s="9">
-        <f>(C4-B4)+1</f>
-        <v>7</v>
-      </c>
-      <c r="E4" s="10"/>
+        <v>46071</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-    </row>
-    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="67">
+        <v>8</v>
+      </c>
+      <c r="T4" s="73">
+        <v>1</v>
+      </c>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+    </row>
+    <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>46082</v>
       </c>
-      <c r="C5" s="13">
-        <v>46087</v>
-      </c>
-      <c r="D5" s="14">
-        <f>(C5-B5)+1</f>
+      <c r="C5" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="68">
         <v>6</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-    </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T5" s="74">
+        <v>1</v>
+      </c>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+    </row>
+    <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="8">
         <v>46078</v>
       </c>
-      <c r="C6" s="8">
-        <v>46087</v>
-      </c>
-      <c r="D6" s="9">
-        <f>(C6-B6)+1</f>
-        <v>10</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="10"/>
+      <c r="C6" s="90">
+        <v>46082</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-    </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="67">
+        <v>12</v>
+      </c>
+      <c r="T6" s="73">
+        <v>1</v>
+      </c>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+    </row>
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
+        <v>46082</v>
+      </c>
+      <c r="C7" s="91">
         <v>46088</v>
       </c>
-      <c r="C7" s="13">
-        <v>46088</v>
-      </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="68">
         <v>1</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-    </row>
-    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="T7" s="74">
+        <v>1</v>
+      </c>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-    </row>
-    <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="69">
+        <v>91</v>
+      </c>
+      <c r="T8" s="75">
+        <v>1</v>
+      </c>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+    </row>
+    <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>46089</v>
       </c>
-      <c r="C9" s="13">
-        <v>46094</v>
-      </c>
-      <c r="D9" s="14">
-        <f t="shared" ref="D9:D16" si="0">(C9-B9)+1</f>
+      <c r="C9" s="12">
+        <v>46089</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="68">
         <v>6</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-    </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T9" s="74">
+        <v>1</v>
+      </c>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>31</v>
       </c>
@@ -1326,59 +1696,67 @@
         <v>46089</v>
       </c>
       <c r="C10" s="8">
-        <v>46094</v>
-      </c>
-      <c r="D10" s="9">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-    </row>
-    <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+        <v>46089</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="67">
+        <v>8</v>
+      </c>
+      <c r="T10" s="73">
+        <v>1</v>
+      </c>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>46091</v>
       </c>
-      <c r="C11" s="13">
-        <v>46097</v>
-      </c>
-      <c r="D11" s="14">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-    </row>
-    <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="12">
+        <v>46091</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="68">
+        <v>8</v>
+      </c>
+      <c r="T11" s="74">
+        <v>1</v>
+      </c>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -1386,119 +1764,135 @@
         <v>46095</v>
       </c>
       <c r="C12" s="8">
-        <v>46101</v>
-      </c>
-      <c r="D12" s="9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-    </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+        <v>46095</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="67">
+        <v>15</v>
+      </c>
+      <c r="T12" s="73">
+        <v>1</v>
+      </c>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+    </row>
+    <row r="13" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>46098</v>
       </c>
-      <c r="C13" s="13">
-        <v>46105</v>
-      </c>
-      <c r="D13" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-    </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="12">
+        <v>46098</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="68">
+        <v>20</v>
+      </c>
+      <c r="T13" s="74">
+        <v>1</v>
+      </c>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+    </row>
+    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C14" s="8">
         <v>46107</v>
       </c>
-      <c r="D14" s="9">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-    </row>
-    <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="C14" s="90">
+        <v>46110</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="67">
+        <v>15</v>
+      </c>
+      <c r="T14" s="73">
+        <v>1</v>
+      </c>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+    </row>
+    <row r="15" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>46095</v>
       </c>
-      <c r="C15" s="13">
-        <v>46102</v>
-      </c>
-      <c r="D15" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-    </row>
-    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="12">
+        <v>46095</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="68">
+        <v>10</v>
+      </c>
+      <c r="T15" s="74">
+        <v>1</v>
+      </c>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+    </row>
+    <row r="16" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
@@ -1506,113 +1900,133 @@
         <v>46104</v>
       </c>
       <c r="C16" s="8">
-        <v>46109</v>
-      </c>
-      <c r="D16" s="9">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-    </row>
-    <row r="17" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+        <v>46104</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="67">
+        <v>8</v>
+      </c>
+      <c r="T16" s="73">
+        <v>1</v>
+      </c>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+    </row>
+    <row r="17" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>46110</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="12">
+        <v>46107</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="68">
+        <v>1</v>
+      </c>
+      <c r="T17" s="74">
+        <v>1</v>
+      </c>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+    </row>
+    <row r="18" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="70">
+        <v>92</v>
+      </c>
+      <c r="T18" s="76">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+    </row>
+    <row r="19" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C19" s="12">
         <v>46110</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="68">
+        <v>50</v>
+      </c>
+      <c r="T19" s="74">
         <v>1</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-    </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-    </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="13">
-        <v>46111</v>
-      </c>
-      <c r="C19" s="13">
-        <v>46123</v>
-      </c>
-      <c r="D19" s="14">
-        <f>(C19-B19)+1</f>
-        <v>13</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-    </row>
-    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+    </row>
+    <row r="20" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
@@ -1620,359 +2034,498 @@
         <v>46120</v>
       </c>
       <c r="C20" s="8">
+        <v>46120</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="92">
+        <v>15</v>
+      </c>
+      <c r="T20" s="74">
+        <v>1</v>
+      </c>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+    </row>
+    <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C21" s="12">
+        <v>46126</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="93">
+        <v>10</v>
+      </c>
+      <c r="T21" s="74">
+        <v>1</v>
+      </c>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+    </row>
+    <row r="22" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C22" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="92">
+        <v>10</v>
+      </c>
+      <c r="T22" s="73">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+    </row>
+    <row r="23" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="12">
         <v>46130</v>
       </c>
-      <c r="D20" s="9">
-        <f>(C20-B20)+1</f>
-        <v>11</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-    </row>
-    <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="13">
-        <v>46126</v>
-      </c>
-      <c r="C21" s="13">
-        <v>46134</v>
-      </c>
-      <c r="D21" s="14">
-        <f>(C21-B21)+1</f>
-        <v>9</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-    </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="C23" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="93">
+        <v>10</v>
+      </c>
+      <c r="T23" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+    </row>
+    <row r="24" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C24" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="92">
+        <v>1</v>
+      </c>
+      <c r="T24" s="73">
+        <v>1</v>
+      </c>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+    </row>
+    <row r="25" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="8">
-        <v>46132</v>
-      </c>
-      <c r="C22" s="8">
-        <v>46137</v>
-      </c>
-      <c r="D22" s="9">
-        <f>(C22-B22)+1</f>
+      <c r="B25" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C25" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="68">
+        <v>10</v>
+      </c>
+      <c r="T25" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+    </row>
+    <row r="26" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="12">
+        <v>46138</v>
+      </c>
+      <c r="C26" s="12">
+        <v>46138</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="67">
         <v>6</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-    </row>
-    <row r="23" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="13">
-        <v>46138</v>
-      </c>
-      <c r="C23" s="13">
-        <v>46138</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="T26" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+    </row>
+    <row r="27" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="71">
+        <v>48</v>
+      </c>
+      <c r="T27" s="80">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+    </row>
+    <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="68">
+        <v>6</v>
+      </c>
+      <c r="T28" s="79">
+        <v>0</v>
+      </c>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+    </row>
+    <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46143</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="67">
+        <v>8</v>
+      </c>
+      <c r="T29" s="81">
+        <v>0</v>
+      </c>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+    </row>
+    <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="12">
+        <v>46147</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="68">
+        <v>20</v>
+      </c>
+      <c r="T30" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+    </row>
+    <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46160</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="67">
+        <v>5</v>
+      </c>
+      <c r="T31" s="81">
+        <v>0</v>
+      </c>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+    </row>
+    <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="12">
+        <v>46164</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="68">
+        <v>8</v>
+      </c>
+      <c r="T32" s="79">
+        <v>0</v>
+      </c>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+    </row>
+    <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46173</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="S33" s="67">
         <v>1</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-    </row>
-    <row r="24" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-    </row>
-    <row r="25" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="13">
-        <v>46139</v>
-      </c>
-      <c r="C25" s="13">
-        <v>46146</v>
-      </c>
-      <c r="D25" s="14">
-        <f>(C25-B25)+1</f>
-        <v>8</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-    </row>
-    <row r="26" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46143</v>
-      </c>
-      <c r="C26" s="8">
-        <v>46152</v>
-      </c>
-      <c r="D26" s="9">
-        <f>(C26-B26)+1</f>
-        <v>10</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-    </row>
-    <row r="27" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="13">
-        <v>46147</v>
-      </c>
-      <c r="C27" s="13">
-        <v>46163</v>
-      </c>
-      <c r="D27" s="14">
-        <f>(C27-B27)+1</f>
-        <v>17</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="15"/>
-    </row>
-    <row r="28" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46160</v>
-      </c>
-      <c r="C28" s="8">
-        <v>46169</v>
-      </c>
-      <c r="D28" s="9">
-        <f>(C28-B28)+1</f>
-        <v>10</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-    </row>
-    <row r="29" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="13">
-        <v>46164</v>
-      </c>
-      <c r="C29" s="13">
-        <v>46172</v>
-      </c>
-      <c r="D29" s="14">
-        <f>(C29-B29)+1</f>
-        <v>9</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-    </row>
-    <row r="30" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="8">
-        <v>46173</v>
-      </c>
-      <c r="C30" s="8">
-        <v>46173</v>
-      </c>
-      <c r="D30" s="9">
-        <v>1</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="T33" s="81">
+        <v>0</v>
+      </c>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="32" t="s">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="33" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="31" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="32" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="35" t="s">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="34" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1980,308 +2533,777 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B5804F-7137-4386-BFF7-F59B6D2ED32C}">
+  <dimension ref="B1:F41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46071</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46071</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D5" s="12">
+        <v>46082</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46078</v>
+      </c>
+      <c r="D6" s="90">
+        <v>46082</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D7" s="91">
+        <v>46088</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46089</v>
+      </c>
+      <c r="D9" s="12">
+        <v>46089</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="8">
+        <v>46089</v>
+      </c>
+      <c r="D10" s="8">
+        <v>46089</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12">
+        <v>46091</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46091</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="2:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="8">
+        <v>46095</v>
+      </c>
+      <c r="D12" s="8">
+        <v>46095</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="88" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="57" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="12">
+        <v>46098</v>
+      </c>
+      <c r="D13" s="12">
+        <v>46098</v>
+      </c>
+      <c r="E13" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="89" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="8">
+        <v>46107</v>
+      </c>
+      <c r="D14" s="90">
+        <v>46110</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="12">
+        <v>46095</v>
+      </c>
+      <c r="D15" s="12">
+        <v>46095</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="8">
+        <v>46104</v>
+      </c>
+      <c r="D16" s="8">
+        <v>46104</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="12">
+        <v>46110</v>
+      </c>
+      <c r="D17" s="12">
+        <v>46107</v>
+      </c>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+    </row>
+    <row r="19" spans="2:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="12">
+        <v>46107</v>
+      </c>
+      <c r="D19" s="12">
+        <v>46110</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="8">
+        <v>46120</v>
+      </c>
+      <c r="D20" s="8">
+        <v>46120</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="12">
+        <v>46126</v>
+      </c>
+      <c r="D21" s="12">
+        <v>46126</v>
+      </c>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="2:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D22" s="12">
+        <v>46135</v>
+      </c>
+      <c r="E22" s="87" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="87" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="12">
+        <v>46130</v>
+      </c>
+      <c r="D23" s="12">
+        <v>46135</v>
+      </c>
+      <c r="E23" s="87"/>
+      <c r="F23" s="86"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D24" s="12">
+        <v>46135</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="12">
+        <v>46135</v>
+      </c>
+      <c r="D25" s="12">
+        <v>46135</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="12">
+        <v>46138</v>
+      </c>
+      <c r="D26" s="12">
+        <v>46138</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="12">
+        <v>46139</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="8">
+        <v>46143</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="2:6" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="12">
+        <v>46147</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="89" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46160</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="12">
+        <v>46164</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46173</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D06FBD7-028B-499E-9E9C-2C08DD147AE3}">
   <dimension ref="B4:S34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="37"/>
-    <col min="2" max="2" width="30.5546875" style="37" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="37" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="37"/>
-    <col min="6" max="12" width="2" style="37" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="37"/>
+    <col min="1" max="1" width="11.5546875" style="35"/>
+    <col min="2" max="2" width="30.5546875" style="35" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="35" customWidth="1"/>
+    <col min="4" max="5" width="11.5546875" style="35"/>
+    <col min="6" max="12" width="2" style="35" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="35"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="F4" s="63" t="s">
+      <c r="F4" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63" t="s">
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53" t="s">
+      <c r="C5" s="51"/>
+      <c r="D5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="50" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="51"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="48"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
     </row>
     <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="47">
+      <c r="C8" s="58"/>
+      <c r="D8" s="45">
         <v>46071</v>
       </c>
-      <c r="E8" s="46"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="47">
+      <c r="C9" s="58"/>
+      <c r="D9" s="45">
         <v>46082</v>
       </c>
-      <c r="E9" s="46"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="47">
+      <c r="C10" s="58"/>
+      <c r="D10" s="45">
         <v>46078</v>
       </c>
-      <c r="E10" s="46"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="47">
+      <c r="C11" s="58"/>
+      <c r="D11" s="45">
         <v>46088</v>
       </c>
-      <c r="E11" s="46"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="44"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="42"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="44"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="42"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="42"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="62"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="44"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="44"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="42"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="44"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="42"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="44"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="44"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="42"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="44"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="42"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="41"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="39"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="41"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="39"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="41"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="41"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="39"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="39"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="38"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="36"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="38"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="36"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="38"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="36"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="36"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="36"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -2323,11 +3345,282 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2866052E-4078-4146-9B86-B8CA4EDD3A6C}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F118CF6-763D-482D-95FF-92FD464E16EE}">
+  <dimension ref="B3:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="82" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="82" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="82" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="82" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="84">
+        <v>46071</v>
+      </c>
+      <c r="E4" s="84">
+        <v>46077</v>
+      </c>
+      <c r="F4" s="83">
+        <v>7</v>
+      </c>
+      <c r="G4" s="83">
+        <v>20</v>
+      </c>
+      <c r="H4" s="85">
+        <v>1</v>
+      </c>
+      <c r="I4" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B5" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="84">
+        <v>46082</v>
+      </c>
+      <c r="E5" s="84">
+        <v>46087</v>
+      </c>
+      <c r="F5" s="83">
+        <v>6</v>
+      </c>
+      <c r="G5" s="83">
+        <v>18</v>
+      </c>
+      <c r="H5" s="85">
+        <v>1</v>
+      </c>
+      <c r="I5" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B6" s="83" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="84">
+        <v>46095</v>
+      </c>
+      <c r="E6" s="84">
+        <v>46101</v>
+      </c>
+      <c r="F6" s="83">
+        <v>7</v>
+      </c>
+      <c r="G6" s="83">
+        <v>25</v>
+      </c>
+      <c r="H6" s="85">
+        <v>1</v>
+      </c>
+      <c r="I6" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="83" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="84">
+        <v>46099</v>
+      </c>
+      <c r="E7" s="84">
+        <v>46107</v>
+      </c>
+      <c r="F7" s="83">
+        <v>9</v>
+      </c>
+      <c r="G7" s="83">
+        <v>30</v>
+      </c>
+      <c r="H7" s="85">
+        <v>1</v>
+      </c>
+      <c r="I7" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="J7" s="83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="B8" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="84">
+        <v>46099</v>
+      </c>
+      <c r="E8" s="84">
+        <v>46107</v>
+      </c>
+      <c r="F8" s="83">
+        <v>9</v>
+      </c>
+      <c r="G8" s="83">
+        <v>30</v>
+      </c>
+      <c r="H8" s="85">
+        <v>1</v>
+      </c>
+      <c r="I8" s="83" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="83" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="B9" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="84">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="84">
+        <v>46130</v>
+      </c>
+      <c r="F9" s="83">
+        <v>11</v>
+      </c>
+      <c r="G9" s="83">
+        <v>20</v>
+      </c>
+      <c r="H9" s="85">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="83" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="83" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="83" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="84">
+        <v>46147</v>
+      </c>
+      <c r="E10" s="84">
+        <v>46163</v>
+      </c>
+      <c r="F10" s="83">
+        <v>17</v>
+      </c>
+      <c r="G10" s="83">
+        <v>40</v>
+      </c>
+      <c r="H10" s="85">
+        <v>0.6</v>
+      </c>
+      <c r="I10" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" s="83" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="B11" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="84">
+        <v>46165</v>
+      </c>
+      <c r="E11" s="84">
+        <v>46172</v>
+      </c>
+      <c r="F11" s="83">
+        <v>9</v>
+      </c>
+      <c r="G11" s="83">
+        <v>15</v>
+      </c>
+      <c r="H11" s="85">
+        <v>0</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" s="83" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/gantt_tfm_completo.xlsx
+++ b/gantt_tfm_completo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/97B404005393A13D/tfm/planify-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA78810-EA29-4848-BD19-BFD7265F6621}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327512D3-D7FA-4B4E-83C5-06BA2BF6A3D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="122">
   <si>
     <t>Descripción del hito</t>
   </si>
@@ -409,6 +409,9 @@
   </si>
   <si>
     <t>Inicio real</t>
+  </si>
+  <si>
+    <t>Activar logs en Render</t>
   </si>
 </sst>
 </file>
@@ -952,6 +955,109 @@
     <xf numFmtId="0" fontId="8" fillId="24" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -969,109 +1075,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1160,10 +1163,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1366,39 +1365,39 @@
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63" t="s">
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64" t="s">
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="64" t="s">
+      <c r="T1" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="64" t="s">
+      <c r="U1" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="V1" s="64" t="s">
+      <c r="V1" s="53" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1451,10 +1450,10 @@
       <c r="R2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
     </row>
     <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1477,10 +1476,10 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="66">
+      <c r="S3" s="55">
         <v>27</v>
       </c>
-      <c r="T3" s="72">
+      <c r="T3" s="61">
         <v>1</v>
       </c>
       <c r="U3" s="6"/>
@@ -1511,10 +1510,10 @@
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
-      <c r="S4" s="67">
+      <c r="S4" s="56">
         <v>8</v>
       </c>
-      <c r="T4" s="73">
+      <c r="T4" s="62">
         <v>1</v>
       </c>
       <c r="U4" s="10"/>
@@ -1545,10 +1544,10 @@
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
-      <c r="S5" s="68">
+      <c r="S5" s="57">
         <v>6</v>
       </c>
-      <c r="T5" s="74">
+      <c r="T5" s="63">
         <v>1</v>
       </c>
       <c r="U5" s="13"/>
@@ -1561,7 +1560,7 @@
       <c r="B6" s="8">
         <v>46078</v>
       </c>
-      <c r="C6" s="90">
+      <c r="C6" s="79">
         <v>46082</v>
       </c>
       <c r="D6" s="10"/>
@@ -1579,10 +1578,10 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="67">
+      <c r="S6" s="56">
         <v>12</v>
       </c>
-      <c r="T6" s="73">
+      <c r="T6" s="62">
         <v>1</v>
       </c>
       <c r="U6" s="10"/>
@@ -1595,7 +1594,7 @@
       <c r="B7" s="12">
         <v>46082</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="80">
         <v>46088</v>
       </c>
       <c r="D7" s="13"/>
@@ -1615,10 +1614,10 @@
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
-      <c r="S7" s="68">
+      <c r="S7" s="57">
         <v>1</v>
       </c>
-      <c r="T7" s="74">
+      <c r="T7" s="63">
         <v>1</v>
       </c>
       <c r="U7" s="13"/>
@@ -1645,10 +1644,10 @@
       <c r="P8" s="18"/>
       <c r="Q8" s="18"/>
       <c r="R8" s="18"/>
-      <c r="S8" s="69">
+      <c r="S8" s="58">
         <v>91</v>
       </c>
-      <c r="T8" s="75">
+      <c r="T8" s="64">
         <v>1</v>
       </c>
       <c r="U8" s="18"/>
@@ -1679,10 +1678,10 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
-      <c r="S9" s="68">
+      <c r="S9" s="57">
         <v>6</v>
       </c>
-      <c r="T9" s="74">
+      <c r="T9" s="63">
         <v>1</v>
       </c>
       <c r="U9" s="13"/>
@@ -1713,10 +1712,10 @@
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
-      <c r="S10" s="67">
+      <c r="S10" s="56">
         <v>8</v>
       </c>
-      <c r="T10" s="73">
+      <c r="T10" s="62">
         <v>1</v>
       </c>
       <c r="U10" s="10"/>
@@ -1747,10 +1746,10 @@
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
-      <c r="S11" s="68">
+      <c r="S11" s="57">
         <v>8</v>
       </c>
-      <c r="T11" s="74">
+      <c r="T11" s="63">
         <v>1</v>
       </c>
       <c r="U11" s="13"/>
@@ -1781,10 +1780,10 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
-      <c r="S12" s="67">
+      <c r="S12" s="56">
         <v>15</v>
       </c>
-      <c r="T12" s="73">
+      <c r="T12" s="62">
         <v>1</v>
       </c>
       <c r="U12" s="10"/>
@@ -1815,10 +1814,10 @@
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
-      <c r="S13" s="68">
+      <c r="S13" s="57">
         <v>20</v>
       </c>
-      <c r="T13" s="74">
+      <c r="T13" s="63">
         <v>1</v>
       </c>
       <c r="U13" s="13"/>
@@ -1831,7 +1830,7 @@
       <c r="B14" s="8">
         <v>46107</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="79">
         <v>46110</v>
       </c>
       <c r="D14" s="10"/>
@@ -1849,10 +1848,10 @@
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
-      <c r="S14" s="67">
+      <c r="S14" s="56">
         <v>15</v>
       </c>
-      <c r="T14" s="73">
+      <c r="T14" s="62">
         <v>1</v>
       </c>
       <c r="U14" s="10"/>
@@ -1883,10 +1882,10 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
-      <c r="S15" s="68">
+      <c r="S15" s="57">
         <v>10</v>
       </c>
-      <c r="T15" s="74">
+      <c r="T15" s="63">
         <v>1</v>
       </c>
       <c r="U15" s="13"/>
@@ -1917,10 +1916,10 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="67">
+      <c r="S16" s="56">
         <v>8</v>
       </c>
-      <c r="T16" s="73">
+      <c r="T16" s="62">
         <v>1</v>
       </c>
       <c r="U16" s="10"/>
@@ -1953,10 +1952,10 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="13"/>
-      <c r="S17" s="68">
+      <c r="S17" s="57">
         <v>1</v>
       </c>
-      <c r="T17" s="74">
+      <c r="T17" s="63">
         <v>1</v>
       </c>
       <c r="U17" s="13"/>
@@ -1983,10 +1982,10 @@
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
       <c r="R18" s="22"/>
-      <c r="S18" s="70">
+      <c r="S18" s="59">
         <v>92</v>
       </c>
-      <c r="T18" s="76">
+      <c r="T18" s="65">
         <v>0.71666666666666667</v>
       </c>
       <c r="U18" s="22"/>
@@ -2017,10 +2016,10 @@
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
-      <c r="S19" s="68">
+      <c r="S19" s="57">
         <v>50</v>
       </c>
-      <c r="T19" s="74">
+      <c r="T19" s="63">
         <v>1</v>
       </c>
       <c r="U19" s="13"/>
@@ -2051,10 +2050,10 @@
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
-      <c r="S20" s="92">
+      <c r="S20" s="81">
         <v>15</v>
       </c>
-      <c r="T20" s="74">
+      <c r="T20" s="63">
         <v>1</v>
       </c>
       <c r="U20" s="10"/>
@@ -2085,10 +2084,10 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="93">
+      <c r="S21" s="82">
         <v>10</v>
       </c>
-      <c r="T21" s="74">
+      <c r="T21" s="63">
         <v>1</v>
       </c>
       <c r="U21" s="13"/>
@@ -2119,10 +2118,10 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-      <c r="S22" s="92">
+      <c r="S22" s="81">
         <v>10</v>
       </c>
-      <c r="T22" s="73">
+      <c r="T22" s="62">
         <v>1</v>
       </c>
       <c r="U22" s="10"/>
@@ -2153,10 +2152,10 @@
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-      <c r="S23" s="93">
+      <c r="S23" s="82">
         <v>10</v>
       </c>
-      <c r="T23" s="78">
+      <c r="T23" s="67">
         <v>0.5</v>
       </c>
       <c r="U23" s="13"/>
@@ -2187,10 +2186,10 @@
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-      <c r="S24" s="92">
+      <c r="S24" s="81">
         <v>1</v>
       </c>
-      <c r="T24" s="73">
+      <c r="T24" s="62">
         <v>1</v>
       </c>
       <c r="U24" s="10"/>
@@ -2221,10 +2220,10 @@
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
-      <c r="S25" s="68">
+      <c r="S25" s="57">
         <v>10</v>
       </c>
-      <c r="T25" s="77">
+      <c r="T25" s="66">
         <v>0.8</v>
       </c>
       <c r="U25" s="13"/>
@@ -2257,10 +2256,10 @@
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
-      <c r="S26" s="67">
+      <c r="S26" s="56">
         <v>6</v>
       </c>
-      <c r="T26" s="78">
+      <c r="T26" s="67">
         <v>0.5</v>
       </c>
       <c r="U26" s="10"/>
@@ -2287,10 +2286,10 @@
       <c r="P27" s="26"/>
       <c r="Q27" s="26"/>
       <c r="R27" s="26"/>
-      <c r="S27" s="71">
+      <c r="S27" s="60">
         <v>48</v>
       </c>
-      <c r="T27" s="80">
+      <c r="T27" s="69">
         <v>0.13333333333333333</v>
       </c>
       <c r="U27" s="26"/>
@@ -2319,10 +2318,10 @@
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
-      <c r="S28" s="68">
+      <c r="S28" s="57">
         <v>6</v>
       </c>
-      <c r="T28" s="79">
+      <c r="T28" s="68">
         <v>0</v>
       </c>
       <c r="U28" s="10"/>
@@ -2351,10 +2350,10 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
-      <c r="S29" s="67">
+      <c r="S29" s="56">
         <v>8</v>
       </c>
-      <c r="T29" s="81">
+      <c r="T29" s="70">
         <v>0</v>
       </c>
       <c r="U29" s="13"/>
@@ -2383,10 +2382,10 @@
       <c r="P30" s="27"/>
       <c r="Q30" s="27"/>
       <c r="R30" s="13"/>
-      <c r="S30" s="68">
+      <c r="S30" s="57">
         <v>20</v>
       </c>
-      <c r="T30" s="77">
+      <c r="T30" s="66">
         <v>0.8</v>
       </c>
       <c r="U30" s="10"/>
@@ -2415,10 +2414,10 @@
       <c r="P31" s="10"/>
       <c r="Q31" s="27"/>
       <c r="R31" s="27"/>
-      <c r="S31" s="67">
+      <c r="S31" s="56">
         <v>5</v>
       </c>
-      <c r="T31" s="81">
+      <c r="T31" s="70">
         <v>0</v>
       </c>
       <c r="U31" s="13"/>
@@ -2447,10 +2446,10 @@
       <c r="P32" s="13"/>
       <c r="Q32" s="27"/>
       <c r="R32" s="27"/>
-      <c r="S32" s="68">
+      <c r="S32" s="57">
         <v>8</v>
       </c>
-      <c r="T32" s="79">
+      <c r="T32" s="68">
         <v>0</v>
       </c>
       <c r="U32" s="10"/>
@@ -2481,10 +2480,10 @@
       <c r="R33" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="S33" s="67">
+      <c r="S33" s="56">
         <v>1</v>
       </c>
-      <c r="T33" s="81">
+      <c r="T33" s="70">
         <v>0</v>
       </c>
       <c r="U33" s="13"/>
@@ -2553,10 +2552,10 @@
       <c r="D1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="53" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2609,7 +2608,7 @@
       <c r="C6" s="8">
         <v>46078</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="79">
         <v>46082</v>
       </c>
       <c r="E6" s="10"/>
@@ -2622,7 +2621,7 @@
       <c r="C7" s="12">
         <v>46082</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="80">
         <v>46088</v>
       </c>
       <c r="E7" s="13"/>
@@ -2676,7 +2675,7 @@
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="2:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2686,10 +2685,10 @@
       <c r="D12" s="8">
         <v>46095</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="77" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2703,10 +2702,10 @@
       <c r="D13" s="12">
         <v>46098</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="78" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2717,13 +2716,13 @@
       <c r="C14" s="8">
         <v>46107</v>
       </c>
-      <c r="D14" s="90">
+      <c r="D14" s="79">
         <v>46110</v>
       </c>
-      <c r="E14" s="88" t="s">
+      <c r="E14" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="77" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2785,10 +2784,10 @@
       <c r="D19" s="12">
         <v>46110</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="88" t="s">
+      <c r="F19" s="77" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2818,7 +2817,7 @@
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
     </row>
-    <row r="22" spans="2:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
         <v>117</v>
       </c>
@@ -2828,11 +2827,11 @@
       <c r="D22" s="12">
         <v>46135</v>
       </c>
-      <c r="E22" s="87" t="s">
+      <c r="E22" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="87" t="s">
-        <v>108</v>
+      <c r="F22" s="76" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -2845,8 +2844,8 @@
       <c r="D23" s="12">
         <v>46135</v>
       </c>
-      <c r="E23" s="87"/>
-      <c r="F23" s="86"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="75"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
@@ -2926,10 +2925,10 @@
         <v>46147</v>
       </c>
       <c r="D30" s="12"/>
-      <c r="E30" s="89" t="s">
+      <c r="E30" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="89" t="s">
+      <c r="F30" s="78" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3015,24 +3014,24 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61" t="s">
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="84"/>
+      <c r="S4" s="84"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="52" t="s">
@@ -3074,170 +3073,170 @@
       <c r="E6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
     </row>
     <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="45">
         <v>46071</v>
       </c>
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="58"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="45">
         <v>46082</v>
       </c>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="45">
         <v>46078</v>
       </c>
       <c r="E10" s="44"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="58"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="45">
         <v>46088</v>
       </c>
       <c r="E11" s="44"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="60"/>
+      <c r="C13" s="87"/>
       <c r="D13" s="43"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="60"/>
+      <c r="C14" s="87"/>
       <c r="D14" s="43"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="60"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="43"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="60"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="43"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="60"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="43"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="60"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="43"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="60"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="43"/>
       <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="60" t="s">
+      <c r="B20" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="60"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="43"/>
       <c r="E20" s="42"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="60"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="43"/>
       <c r="E21" s="42"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="40"/>
       <c r="E23" s="39"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="62"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="40"/>
       <c r="E24" s="39"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="62"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="40"/>
       <c r="E25" s="39"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="62"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="40"/>
       <c r="E26" s="39"/>
     </row>
@@ -3250,50 +3249,50 @@
       <c r="E27" s="39"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="59"/>
+      <c r="C29" s="86"/>
       <c r="D29" s="37"/>
       <c r="E29" s="36"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="59"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="37"/>
       <c r="E30" s="36"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="59"/>
+      <c r="C31" s="86"/>
       <c r="D31" s="37"/>
       <c r="E31" s="36"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="59"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="37"/>
       <c r="E32" s="36"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="59"/>
+      <c r="C33" s="86"/>
       <c r="D33" s="37"/>
       <c r="E33" s="36"/>
     </row>
@@ -3307,11 +3306,11 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
@@ -3328,13 +3327,13 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{B0C920EC-53AE-4294-A5C9-69715D62E32A}">
@@ -3360,263 +3359,263 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="71" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="84">
+      <c r="D4" s="73">
         <v>46071</v>
       </c>
-      <c r="E4" s="84">
+      <c r="E4" s="73">
         <v>46077</v>
       </c>
-      <c r="F4" s="83">
+      <c r="F4" s="72">
         <v>7</v>
       </c>
-      <c r="G4" s="83">
+      <c r="G4" s="72">
         <v>20</v>
       </c>
-      <c r="H4" s="85">
+      <c r="H4" s="74">
         <v>1</v>
       </c>
-      <c r="I4" s="83" t="s">
+      <c r="I4" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="83" t="s">
+      <c r="J4" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="83" t="s">
+      <c r="C5" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="73">
         <v>46082</v>
       </c>
-      <c r="E5" s="84">
+      <c r="E5" s="73">
         <v>46087</v>
       </c>
-      <c r="F5" s="83">
+      <c r="F5" s="72">
         <v>6</v>
       </c>
-      <c r="G5" s="83">
+      <c r="G5" s="72">
         <v>18</v>
       </c>
-      <c r="H5" s="85">
+      <c r="H5" s="74">
         <v>1</v>
       </c>
-      <c r="I5" s="83" t="s">
+      <c r="I5" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="83" t="s">
+      <c r="J5" s="72" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="84">
+      <c r="D6" s="73">
         <v>46095</v>
       </c>
-      <c r="E6" s="84">
+      <c r="E6" s="73">
         <v>46101</v>
       </c>
-      <c r="F6" s="83">
+      <c r="F6" s="72">
         <v>7</v>
       </c>
-      <c r="G6" s="83">
+      <c r="G6" s="72">
         <v>25</v>
       </c>
-      <c r="H6" s="85">
+      <c r="H6" s="74">
         <v>1</v>
       </c>
-      <c r="I6" s="83" t="s">
+      <c r="I6" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="83" t="s">
+      <c r="J6" s="72" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="84">
+      <c r="D7" s="73">
         <v>46099</v>
       </c>
-      <c r="E7" s="84">
+      <c r="E7" s="73">
         <v>46107</v>
       </c>
-      <c r="F7" s="83">
+      <c r="F7" s="72">
         <v>9</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="72">
         <v>30</v>
       </c>
-      <c r="H7" s="85">
+      <c r="H7" s="74">
         <v>1</v>
       </c>
-      <c r="I7" s="83" t="s">
+      <c r="I7" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="J7" s="83" t="s">
+      <c r="J7" s="72" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="73">
         <v>46099</v>
       </c>
-      <c r="E8" s="84">
+      <c r="E8" s="73">
         <v>46107</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="72">
         <v>9</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="72">
         <v>30</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="74">
         <v>1</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="83" t="s">
+      <c r="J8" s="72" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="73">
         <v>46120</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="73">
         <v>46130</v>
       </c>
-      <c r="F9" s="83">
+      <c r="F9" s="72">
         <v>11</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="72">
         <v>20</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="74">
         <v>0.8</v>
       </c>
-      <c r="I9" s="83" t="s">
+      <c r="I9" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="83" t="s">
+      <c r="J9" s="72" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="73">
         <v>46147</v>
       </c>
-      <c r="E10" s="84">
+      <c r="E10" s="73">
         <v>46163</v>
       </c>
-      <c r="F10" s="83">
+      <c r="F10" s="72">
         <v>17</v>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="72">
         <v>40</v>
       </c>
-      <c r="H10" s="85">
+      <c r="H10" s="74">
         <v>0.6</v>
       </c>
-      <c r="I10" s="83" t="s">
+      <c r="I10" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="83" t="s">
+      <c r="J10" s="72" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="73">
         <v>46165</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="73">
         <v>46172</v>
       </c>
-      <c r="F11" s="83">
+      <c r="F11" s="72">
         <v>9</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="72">
         <v>15</v>
       </c>
-      <c r="H11" s="85">
+      <c r="H11" s="74">
         <v>0</v>
       </c>
-      <c r="I11" s="83" t="s">
+      <c r="I11" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="83" t="s">
+      <c r="J11" s="72" t="s">
         <v>116</v>
       </c>
     </row>

--- a/gantt_tfm_completo.xlsx
+++ b/gantt_tfm_completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/97B404005393A13D/tfm/planify-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327512D3-D7FA-4B4E-83C5-06BA2BF6A3D4}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C740BBA-CD53-4203-8009-D9450C859771}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama de Gantt" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
   <si>
     <t>Descripción del hito</t>
   </si>
@@ -412,6 +412,177 @@
   </si>
   <si>
     <t>Activar logs en Render</t>
+  </si>
+  <si>
+    <t>Identificador</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Dependencias</t>
+  </si>
+  <si>
+    <t>Inicio estimado</t>
+  </si>
+  <si>
+    <t>Fin estimado</t>
+  </si>
+  <si>
+    <t>Fin real</t>
+  </si>
+  <si>
+    <t>Avance (%)</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Estudio, análisis y evaluación de objetivos y resultados esperados</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Análisis de herramientas disponibles y definición del MVP</t>
+  </si>
+  <si>
+    <t>1.3.1</t>
+  </si>
+  <si>
+    <t>Elaboración de documentación inicial y entrega PEC1</t>
+  </si>
+  <si>
+    <t>1.1, 1.2</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Benchmarking y análisis de mercado</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Estudio de arquitectura de la aplicación</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Desarrollo de base de datos PostgreSQL</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Desarrollo backend con Node.js y autenticación JWT</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Desarrollo frontend con Angular (estructura base)</t>
+  </si>
+  <si>
+    <t>2.6.1</t>
+  </si>
+  <si>
+    <t>Elaboración wireframes y estudio UI</t>
+  </si>
+  <si>
+    <t>2.6.2</t>
+  </si>
+  <si>
+    <t>Elaboración documentación y entrega PEC2</t>
+  </si>
+  <si>
+    <t>2.3, 2.5</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Análisis entregables PEC3</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Desarrollo frontend avanzado (guards, dashboard, CRUD)</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Integración backend-frontend y corrección de errores</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Diseño visual y usabilidad (login, dashboard, calendario)</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Despliegue en servidor público (Render + Netlify)</t>
+  </si>
+  <si>
+    <t>3.6.1</t>
+  </si>
+  <si>
+    <t>Tests unitarios y validación</t>
+  </si>
+  <si>
+    <t>3.6.2</t>
+  </si>
+  <si>
+    <t>Elaboración documentación y entrega PEC3</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Repaso consecución de objetivos y resultados</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Conclusiones del Trabajo Fin de Máster</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Elaboración de la memoria final</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Elaboración presentación en vídeo del TFM</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Preparación defensa del TFM</t>
   </si>
 </sst>
 </file>
@@ -821,7 +992,7 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,35 +1217,38 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1163,6 +1337,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3014,24 +3192,24 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84" t="s">
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="84"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="87"/>
+      <c r="S4" s="87"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="52" t="s">
@@ -3073,170 +3251,170 @@
       <c r="E6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="93" t="s">
+      <c r="B8" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="93"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="45">
         <v>46071</v>
       </c>
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="93" t="s">
+      <c r="B9" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="93"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="45">
         <v>46082</v>
       </c>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="93" t="s">
+      <c r="B10" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="93"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="45">
         <v>46078</v>
       </c>
       <c r="E10" s="44"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="93"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="45">
         <v>46088</v>
       </c>
       <c r="E11" s="44"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="87"/>
+      <c r="C13" s="88"/>
       <c r="D13" s="43"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="87"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="43"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="87"/>
+      <c r="C15" s="88"/>
       <c r="D15" s="43"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="43"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="87"/>
+      <c r="C17" s="88"/>
       <c r="D17" s="43"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="87"/>
+      <c r="C18" s="88"/>
       <c r="D18" s="43"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="87"/>
+      <c r="C19" s="88"/>
       <c r="D19" s="43"/>
       <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="87"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="43"/>
       <c r="E20" s="42"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="87"/>
+      <c r="C21" s="88"/>
       <c r="D21" s="43"/>
       <c r="E21" s="42"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="91" t="s">
+      <c r="B22" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="85"/>
+      <c r="C23" s="91"/>
       <c r="D23" s="40"/>
       <c r="E23" s="39"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="85"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="40"/>
       <c r="E24" s="39"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="85"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="40"/>
       <c r="E25" s="39"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="85"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="40"/>
       <c r="E26" s="39"/>
     </row>
@@ -3249,12 +3427,12 @@
       <c r="E27" s="39"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="92" t="s">
+      <c r="B28" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="86" t="s">
@@ -3306,11 +3484,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B22:E22"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
@@ -3327,13 +3507,11 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{B0C920EC-53AE-4294-A5C9-69715D62E32A}">
@@ -3346,9 +3524,611 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2866052E-4078-4146-9B86-B8CA4EDD3A6C}">
-  <dimension ref="A1"/>
+  <dimension ref="B43:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="43" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B43" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="H43" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="71" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B44" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="73">
+        <v>46071</v>
+      </c>
+      <c r="F44" s="73">
+        <v>46071</v>
+      </c>
+      <c r="G44" s="73">
+        <v>46078</v>
+      </c>
+      <c r="H44" s="73">
+        <v>46078</v>
+      </c>
+      <c r="I44" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B45" s="94" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="73">
+        <v>46079</v>
+      </c>
+      <c r="F45" s="73">
+        <v>46079</v>
+      </c>
+      <c r="G45" s="73">
+        <v>46082</v>
+      </c>
+      <c r="H45" s="73">
+        <v>46082</v>
+      </c>
+      <c r="I45" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B46" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" s="73">
+        <v>46083</v>
+      </c>
+      <c r="F46" s="73">
+        <v>46083</v>
+      </c>
+      <c r="G46" s="73">
+        <v>46088</v>
+      </c>
+      <c r="H46" s="73">
+        <v>46088</v>
+      </c>
+      <c r="I46" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B47" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="73">
+        <v>46089</v>
+      </c>
+      <c r="F47" s="73">
+        <v>46089</v>
+      </c>
+      <c r="G47" s="73">
+        <v>46091</v>
+      </c>
+      <c r="H47" s="73">
+        <v>46091</v>
+      </c>
+      <c r="I47" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B48" s="94" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="73">
+        <v>46092</v>
+      </c>
+      <c r="F48" s="73">
+        <v>46092</v>
+      </c>
+      <c r="G48" s="73">
+        <v>46095</v>
+      </c>
+      <c r="H48" s="73">
+        <v>46095</v>
+      </c>
+      <c r="I48" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B49" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" s="72" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="73">
+        <v>46095</v>
+      </c>
+      <c r="F49" s="73">
+        <v>46095</v>
+      </c>
+      <c r="G49" s="73">
+        <v>46098</v>
+      </c>
+      <c r="H49" s="73">
+        <v>46098</v>
+      </c>
+      <c r="I49" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B50" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" s="73">
+        <v>46098</v>
+      </c>
+      <c r="F50" s="73">
+        <v>46098</v>
+      </c>
+      <c r="G50" s="73">
+        <v>46104</v>
+      </c>
+      <c r="H50" s="73">
+        <v>46104</v>
+      </c>
+      <c r="I50" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B51" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="72" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" s="73">
+        <v>46105</v>
+      </c>
+      <c r="F51" s="73">
+        <v>46107</v>
+      </c>
+      <c r="G51" s="73">
+        <v>46110</v>
+      </c>
+      <c r="H51" s="73">
+        <v>46110</v>
+      </c>
+      <c r="I51" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B52" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="72" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="73">
+        <v>46095</v>
+      </c>
+      <c r="F52" s="73">
+        <v>46095</v>
+      </c>
+      <c r="G52" s="73">
+        <v>46101</v>
+      </c>
+      <c r="H52" s="73">
+        <v>46101</v>
+      </c>
+      <c r="I52" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B53" s="94" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="D53" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="E53" s="73">
+        <v>46104</v>
+      </c>
+      <c r="F53" s="73">
+        <v>46104</v>
+      </c>
+      <c r="G53" s="73">
+        <v>46107</v>
+      </c>
+      <c r="H53" s="73">
+        <v>46107</v>
+      </c>
+      <c r="I53" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B54" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="D54" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="73">
+        <v>46108</v>
+      </c>
+      <c r="F54" s="73">
+        <v>46108</v>
+      </c>
+      <c r="G54" s="73">
+        <v>46110</v>
+      </c>
+      <c r="H54" s="73">
+        <v>46110</v>
+      </c>
+      <c r="I54" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B55" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="72" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="73">
+        <v>46111</v>
+      </c>
+      <c r="F55" s="73">
+        <v>46111</v>
+      </c>
+      <c r="G55" s="73">
+        <v>46120</v>
+      </c>
+      <c r="H55" s="73">
+        <v>46120</v>
+      </c>
+      <c r="I55" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B56" s="94" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="72" t="s">
+        <v>156</v>
+      </c>
+      <c r="E56" s="73">
+        <v>46121</v>
+      </c>
+      <c r="F56" s="73">
+        <v>46121</v>
+      </c>
+      <c r="G56" s="73">
+        <v>46126</v>
+      </c>
+      <c r="H56" s="73">
+        <v>46126</v>
+      </c>
+      <c r="I56" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B57" s="94" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="73">
+        <v>46127</v>
+      </c>
+      <c r="F57" s="73">
+        <v>46127</v>
+      </c>
+      <c r="G57" s="73">
+        <v>46137</v>
+      </c>
+      <c r="H57" s="73">
+        <v>46137</v>
+      </c>
+      <c r="I57" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="B58" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E58" s="73">
+        <v>46135</v>
+      </c>
+      <c r="F58" s="73">
+        <v>46135</v>
+      </c>
+      <c r="G58" s="73">
+        <v>46138</v>
+      </c>
+      <c r="H58" s="73">
+        <v>46138</v>
+      </c>
+      <c r="I58" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B59" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="72" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" s="73">
+        <v>46130</v>
+      </c>
+      <c r="F59" s="73">
+        <v>46135</v>
+      </c>
+      <c r="G59" s="73">
+        <v>46138</v>
+      </c>
+      <c r="H59" s="73">
+        <v>46138</v>
+      </c>
+      <c r="I59" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B60" s="94" t="s">
+        <v>166</v>
+      </c>
+      <c r="C60" s="72" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="72" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="73">
+        <v>46135</v>
+      </c>
+      <c r="F60" s="73">
+        <v>46135</v>
+      </c>
+      <c r="G60" s="73">
+        <v>46138</v>
+      </c>
+      <c r="H60" s="73">
+        <v>46138</v>
+      </c>
+      <c r="I60" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B61" s="94" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="D61" s="72" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" s="73">
+        <v>46139</v>
+      </c>
+      <c r="F61" s="73">
+        <v>46139</v>
+      </c>
+      <c r="G61" s="73">
+        <v>46143</v>
+      </c>
+      <c r="H61" s="73">
+        <v>46143</v>
+      </c>
+      <c r="I61" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B62" s="94" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="72" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="73">
+        <v>46144</v>
+      </c>
+      <c r="F62" s="73">
+        <v>46144</v>
+      </c>
+      <c r="G62" s="73">
+        <v>46147</v>
+      </c>
+      <c r="H62" s="73">
+        <v>46147</v>
+      </c>
+      <c r="I62" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B63" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="72" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="73">
+        <v>46148</v>
+      </c>
+      <c r="F63" s="73">
+        <v>46148</v>
+      </c>
+      <c r="G63" s="73">
+        <v>46157</v>
+      </c>
+      <c r="H63" s="73">
+        <v>46157</v>
+      </c>
+      <c r="I63" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B64" s="94" t="s">
+        <v>175</v>
+      </c>
+      <c r="C64" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" s="73">
+        <v>46160</v>
+      </c>
+      <c r="F64" s="73">
+        <v>46160</v>
+      </c>
+      <c r="G64" s="73">
+        <v>46164</v>
+      </c>
+      <c r="H64" s="73">
+        <v>46164</v>
+      </c>
+      <c r="I64" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B65" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="C65" s="72" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="E65" s="73">
+        <v>46165</v>
+      </c>
+      <c r="F65" s="73">
+        <v>46165</v>
+      </c>
+      <c r="G65" s="73">
+        <v>46173</v>
+      </c>
+      <c r="H65" s="73">
+        <v>46173</v>
+      </c>
+      <c r="I65" s="74">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3445,7 +4225,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>93</v>
       </c>
@@ -3474,7 +4254,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B7" s="72" t="s">
         <v>97</v>
       </c>

--- a/gantt_tfm_completo.xlsx
+++ b/gantt_tfm_completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/97B404005393A13D/tfm/planify-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C740BBA-CD53-4203-8009-D9450C859771}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{82CCC87F-0DF3-4B80-8FF4-9443CC48E493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACD0BDA-2DF0-4955-93C8-E1984B47F516}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama de Gantt" sheetId="1" r:id="rId1"/>
@@ -593,7 +593,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -718,19 +718,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF8B5E00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF999999"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -746,6 +733,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -992,7 +986,7 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1163,22 +1157,7 @@
     <xf numFmtId="9" fontId="15" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1202,16 +1181,16 @@
     <xf numFmtId="14" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1247,9 +1226,10 @@
     <xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="21" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Fecha" xfId="3" xr:uid="{14F1AE08-CE79-47EB-B9B7-150CCE63BCFB}"/>
@@ -1543,29 +1523,29 @@
       <c r="C1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83" t="s">
+      <c r="E1" s="78"/>
+      <c r="F1" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83" t="s">
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
       <c r="S1" s="53" t="s">
         <v>78</v>
       </c>
@@ -1738,7 +1718,7 @@
       <c r="B6" s="8">
         <v>46078</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="74">
         <v>46082</v>
       </c>
       <c r="D6" s="10"/>
@@ -1772,7 +1752,7 @@
       <c r="B7" s="12">
         <v>46082</v>
       </c>
-      <c r="C7" s="80">
+      <c r="C7" s="75">
         <v>46088</v>
       </c>
       <c r="D7" s="13"/>
@@ -2008,7 +1988,7 @@
       <c r="B14" s="8">
         <v>46107</v>
       </c>
-      <c r="C14" s="79">
+      <c r="C14" s="74">
         <v>46110</v>
       </c>
       <c r="D14" s="10"/>
@@ -2164,7 +2144,7 @@
         <v>92</v>
       </c>
       <c r="T18" s="65">
-        <v>0.71666666666666667</v>
+        <v>1</v>
       </c>
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
@@ -2228,7 +2208,7 @@
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
-      <c r="S20" s="81">
+      <c r="S20" s="76">
         <v>15</v>
       </c>
       <c r="T20" s="63">
@@ -2262,7 +2242,7 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="82">
+      <c r="S21" s="77">
         <v>10</v>
       </c>
       <c r="T21" s="63">
@@ -2296,7 +2276,7 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-      <c r="S22" s="81">
+      <c r="S22" s="76">
         <v>10</v>
       </c>
       <c r="T22" s="62">
@@ -2330,11 +2310,11 @@
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-      <c r="S23" s="82">
+      <c r="S23" s="77">
         <v>10</v>
       </c>
-      <c r="T23" s="67">
-        <v>0.5</v>
+      <c r="T23" s="62">
+        <v>1</v>
       </c>
       <c r="U23" s="13"/>
       <c r="V23" s="13"/>
@@ -2364,7 +2344,7 @@
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-      <c r="S24" s="81">
+      <c r="S24" s="76">
         <v>1</v>
       </c>
       <c r="T24" s="62">
@@ -2401,8 +2381,8 @@
       <c r="S25" s="57">
         <v>10</v>
       </c>
-      <c r="T25" s="66">
-        <v>0.8</v>
+      <c r="T25" s="62">
+        <v>1</v>
       </c>
       <c r="U25" s="13"/>
       <c r="V25" s="13"/>
@@ -2437,8 +2417,8 @@
       <c r="S26" s="56">
         <v>6</v>
       </c>
-      <c r="T26" s="67">
-        <v>0.5</v>
+      <c r="T26" s="62">
+        <v>1</v>
       </c>
       <c r="U26" s="10"/>
       <c r="V26" s="10"/>
@@ -2467,8 +2447,8 @@
       <c r="S27" s="60">
         <v>48</v>
       </c>
-      <c r="T27" s="69">
-        <v>0.13333333333333333</v>
+      <c r="T27" s="90">
+        <v>1</v>
       </c>
       <c r="U27" s="26"/>
       <c r="V27" s="26"/>
@@ -2499,8 +2479,8 @@
       <c r="S28" s="57">
         <v>6</v>
       </c>
-      <c r="T28" s="68">
-        <v>0</v>
+      <c r="T28" s="62">
+        <v>1</v>
       </c>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
@@ -2531,8 +2511,8 @@
       <c r="S29" s="56">
         <v>8</v>
       </c>
-      <c r="T29" s="70">
-        <v>0</v>
+      <c r="T29" s="62">
+        <v>1</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13"/>
@@ -2563,8 +2543,8 @@
       <c r="S30" s="57">
         <v>20</v>
       </c>
-      <c r="T30" s="66">
-        <v>0.8</v>
+      <c r="T30" s="62">
+        <v>1</v>
       </c>
       <c r="U30" s="10"/>
       <c r="V30" s="10"/>
@@ -2595,8 +2575,8 @@
       <c r="S31" s="56">
         <v>5</v>
       </c>
-      <c r="T31" s="70">
-        <v>0</v>
+      <c r="T31" s="62">
+        <v>1</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13"/>
@@ -2627,8 +2607,8 @@
       <c r="S32" s="57">
         <v>8</v>
       </c>
-      <c r="T32" s="68">
-        <v>0</v>
+      <c r="T32" s="62">
+        <v>1</v>
       </c>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
@@ -2661,8 +2641,8 @@
       <c r="S33" s="56">
         <v>1</v>
       </c>
-      <c r="T33" s="70">
-        <v>0</v>
+      <c r="T33" s="62">
+        <v>1</v>
       </c>
       <c r="U33" s="13"/>
       <c r="V33" s="13"/>
@@ -2705,7 +2685,7 @@
     <mergeCell ref="O1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2786,7 +2766,7 @@
       <c r="C6" s="8">
         <v>46078</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="74">
         <v>46082</v>
       </c>
       <c r="E6" s="10"/>
@@ -2799,7 +2779,7 @@
       <c r="C7" s="12">
         <v>46082</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="75">
         <v>46088</v>
       </c>
       <c r="E7" s="13"/>
@@ -2863,10 +2843,10 @@
       <c r="D12" s="8">
         <v>46095</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="72" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2880,10 +2860,10 @@
       <c r="D13" s="12">
         <v>46098</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="78" t="s">
+      <c r="F13" s="73" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2894,13 +2874,13 @@
       <c r="C14" s="8">
         <v>46107</v>
       </c>
-      <c r="D14" s="79">
+      <c r="D14" s="74">
         <v>46110</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="72" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2962,10 +2942,10 @@
       <c r="D19" s="12">
         <v>46110</v>
       </c>
-      <c r="E19" s="77" t="s">
+      <c r="E19" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="72" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3005,10 +2985,10 @@
       <c r="D22" s="12">
         <v>46135</v>
       </c>
-      <c r="E22" s="76" t="s">
+      <c r="E22" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="71" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3022,8 +3002,8 @@
       <c r="D23" s="12">
         <v>46135</v>
       </c>
-      <c r="E23" s="76"/>
-      <c r="F23" s="75"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="70"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
@@ -3103,10 +3083,10 @@
         <v>46147</v>
       </c>
       <c r="D30" s="12"/>
-      <c r="E30" s="78" t="s">
+      <c r="E30" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="78" t="s">
+      <c r="F30" s="73" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3192,24 +3172,24 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="F4" s="87" t="s">
+      <c r="F4" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="52" t="s">
@@ -3251,170 +3231,170 @@
       <c r="E6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
     </row>
     <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="85"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="45">
         <v>46071</v>
       </c>
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="85"/>
+      <c r="C9" s="80"/>
       <c r="D9" s="45">
         <v>46082</v>
       </c>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="85"/>
+      <c r="C10" s="80"/>
       <c r="D10" s="45">
         <v>46078</v>
       </c>
       <c r="E10" s="44"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="85"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="45">
         <v>46088</v>
       </c>
       <c r="E11" s="44"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="92" t="s">
+      <c r="B12" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="88"/>
+      <c r="C13" s="83"/>
       <c r="D13" s="43"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="88"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="43"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="88"/>
+      <c r="C15" s="83"/>
       <c r="D15" s="43"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="88"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="43"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="88"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="43"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="88"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="43"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="88"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="43"/>
       <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="88"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="43"/>
       <c r="E20" s="42"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="88"/>
+      <c r="C21" s="83"/>
       <c r="D21" s="43"/>
       <c r="E21" s="42"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="91"/>
+      <c r="C23" s="86"/>
       <c r="D23" s="40"/>
       <c r="E23" s="39"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="91" t="s">
+      <c r="B24" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="91"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="40"/>
       <c r="E24" s="39"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="91"/>
+      <c r="C25" s="86"/>
       <c r="D25" s="40"/>
       <c r="E25" s="39"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="91" t="s">
+      <c r="B26" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="86"/>
       <c r="D26" s="40"/>
       <c r="E26" s="39"/>
     </row>
@@ -3427,50 +3407,50 @@
       <c r="E27" s="39"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="86" t="s">
+      <c r="B29" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="86"/>
+      <c r="C29" s="81"/>
       <c r="D29" s="37"/>
       <c r="E29" s="36"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="86"/>
+      <c r="C30" s="81"/>
       <c r="D30" s="37"/>
       <c r="E30" s="36"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="86"/>
+      <c r="C31" s="81"/>
       <c r="D31" s="37"/>
       <c r="E31" s="36"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="86"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="37"/>
       <c r="E32" s="36"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="86" t="s">
+      <c r="B33" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="86"/>
+      <c r="C33" s="81"/>
       <c r="D33" s="37"/>
       <c r="E33" s="36"/>
     </row>
@@ -3531,600 +3511,600 @@
   </cols>
   <sheetData>
     <row r="43" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B43" s="71" t="s">
+      <c r="B43" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="71" t="s">
+      <c r="C43" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="71" t="s">
+      <c r="D43" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="E43" s="71" t="s">
+      <c r="E43" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="G43" s="71" t="s">
+      <c r="G43" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="H43" s="71" t="s">
+      <c r="H43" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="I43" s="71" t="s">
+      <c r="I43" s="66" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="72" t="s">
+      <c r="C44" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="72" t="s">
+      <c r="D44" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="E44" s="73">
+      <c r="E44" s="68">
         <v>46071</v>
       </c>
-      <c r="F44" s="73">
+      <c r="F44" s="68">
         <v>46071</v>
       </c>
-      <c r="G44" s="73">
+      <c r="G44" s="68">
         <v>46078</v>
       </c>
-      <c r="H44" s="73">
+      <c r="H44" s="68">
         <v>46078</v>
       </c>
-      <c r="I44" s="74">
+      <c r="I44" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B45" s="94" t="s">
+      <c r="B45" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="C45" s="72" t="s">
+      <c r="C45" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="D45" s="72" t="s">
+      <c r="D45" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="E45" s="73">
+      <c r="E45" s="68">
         <v>46079</v>
       </c>
-      <c r="F45" s="73">
+      <c r="F45" s="68">
         <v>46079</v>
       </c>
-      <c r="G45" s="73">
+      <c r="G45" s="68">
         <v>46082</v>
       </c>
-      <c r="H45" s="73">
+      <c r="H45" s="68">
         <v>46082</v>
       </c>
-      <c r="I45" s="74">
+      <c r="I45" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B46" s="94" t="s">
+      <c r="B46" s="89" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="D46" s="72" t="s">
+      <c r="D46" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="E46" s="73">
+      <c r="E46" s="68">
         <v>46083</v>
       </c>
-      <c r="F46" s="73">
+      <c r="F46" s="68">
         <v>46083</v>
       </c>
-      <c r="G46" s="73">
+      <c r="G46" s="68">
         <v>46088</v>
       </c>
-      <c r="H46" s="73">
+      <c r="H46" s="68">
         <v>46088</v>
       </c>
-      <c r="I46" s="74">
+      <c r="I46" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="89" t="s">
         <v>137</v>
       </c>
-      <c r="C47" s="72" t="s">
+      <c r="C47" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="72" t="s">
+      <c r="D47" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="E47" s="73">
+      <c r="E47" s="68">
         <v>46089</v>
       </c>
-      <c r="F47" s="73">
+      <c r="F47" s="68">
         <v>46089</v>
       </c>
-      <c r="G47" s="73">
+      <c r="G47" s="68">
         <v>46091</v>
       </c>
-      <c r="H47" s="73">
+      <c r="H47" s="68">
         <v>46091</v>
       </c>
-      <c r="I47" s="74">
+      <c r="I47" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="72" t="s">
+      <c r="C48" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="D48" s="72" t="s">
+      <c r="D48" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="73">
+      <c r="E48" s="68">
         <v>46092</v>
       </c>
-      <c r="F48" s="73">
+      <c r="F48" s="68">
         <v>46092</v>
       </c>
-      <c r="G48" s="73">
+      <c r="G48" s="68">
         <v>46095</v>
       </c>
-      <c r="H48" s="73">
+      <c r="H48" s="68">
         <v>46095</v>
       </c>
-      <c r="I48" s="74">
+      <c r="I48" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="94" t="s">
+      <c r="B49" s="89" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="72" t="s">
+      <c r="C49" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="D49" s="72" t="s">
+      <c r="D49" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="E49" s="73">
+      <c r="E49" s="68">
         <v>46095</v>
       </c>
-      <c r="F49" s="73">
+      <c r="F49" s="68">
         <v>46095</v>
       </c>
-      <c r="G49" s="73">
+      <c r="G49" s="68">
         <v>46098</v>
       </c>
-      <c r="H49" s="73">
+      <c r="H49" s="68">
         <v>46098</v>
       </c>
-      <c r="I49" s="74">
+      <c r="I49" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="89" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="72" t="s">
+      <c r="D50" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="E50" s="73">
+      <c r="E50" s="68">
         <v>46098</v>
       </c>
-      <c r="F50" s="73">
+      <c r="F50" s="68">
         <v>46098</v>
       </c>
-      <c r="G50" s="73">
+      <c r="G50" s="68">
         <v>46104</v>
       </c>
-      <c r="H50" s="73">
+      <c r="H50" s="68">
         <v>46104</v>
       </c>
-      <c r="I50" s="74">
+      <c r="I50" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B51" s="94" t="s">
+      <c r="B51" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="72" t="s">
+      <c r="C51" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="D51" s="72" t="s">
+      <c r="D51" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="73">
+      <c r="E51" s="68">
         <v>46105</v>
       </c>
-      <c r="F51" s="73">
+      <c r="F51" s="68">
         <v>46107</v>
       </c>
-      <c r="G51" s="73">
+      <c r="G51" s="68">
         <v>46110</v>
       </c>
-      <c r="H51" s="73">
+      <c r="H51" s="68">
         <v>46110</v>
       </c>
-      <c r="I51" s="74">
+      <c r="I51" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B52" s="94" t="s">
+      <c r="B52" s="89" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="72" t="s">
+      <c r="C52" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="D52" s="72" t="s">
+      <c r="D52" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="E52" s="73">
+      <c r="E52" s="68">
         <v>46095</v>
       </c>
-      <c r="F52" s="73">
+      <c r="F52" s="68">
         <v>46095</v>
       </c>
-      <c r="G52" s="73">
+      <c r="G52" s="68">
         <v>46101</v>
       </c>
-      <c r="H52" s="73">
+      <c r="H52" s="68">
         <v>46101</v>
       </c>
-      <c r="I52" s="74">
+      <c r="I52" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="94" t="s">
+      <c r="B53" s="89" t="s">
         <v>150</v>
       </c>
-      <c r="C53" s="72" t="s">
+      <c r="C53" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="D53" s="72" t="s">
+      <c r="D53" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="E53" s="73">
+      <c r="E53" s="68">
         <v>46104</v>
       </c>
-      <c r="F53" s="73">
+      <c r="F53" s="68">
         <v>46104</v>
       </c>
-      <c r="G53" s="73">
+      <c r="G53" s="68">
         <v>46107</v>
       </c>
-      <c r="H53" s="73">
+      <c r="H53" s="68">
         <v>46107</v>
       </c>
-      <c r="I53" s="74">
+      <c r="I53" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B54" s="94" t="s">
+      <c r="B54" s="89" t="s">
         <v>153</v>
       </c>
-      <c r="C54" s="72" t="s">
+      <c r="C54" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="D54" s="72" t="s">
+      <c r="D54" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="73">
+      <c r="E54" s="68">
         <v>46108</v>
       </c>
-      <c r="F54" s="73">
+      <c r="F54" s="68">
         <v>46108</v>
       </c>
-      <c r="G54" s="73">
+      <c r="G54" s="68">
         <v>46110</v>
       </c>
-      <c r="H54" s="73">
+      <c r="H54" s="68">
         <v>46110</v>
       </c>
-      <c r="I54" s="74">
+      <c r="I54" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B55" s="94" t="s">
+      <c r="B55" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="C55" s="72" t="s">
+      <c r="C55" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="D55" s="72" t="s">
+      <c r="D55" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="E55" s="73">
+      <c r="E55" s="68">
         <v>46111</v>
       </c>
-      <c r="F55" s="73">
+      <c r="F55" s="68">
         <v>46111</v>
       </c>
-      <c r="G55" s="73">
+      <c r="G55" s="68">
         <v>46120</v>
       </c>
-      <c r="H55" s="73">
+      <c r="H55" s="68">
         <v>46120</v>
       </c>
-      <c r="I55" s="74">
+      <c r="I55" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B56" s="94" t="s">
+      <c r="B56" s="89" t="s">
         <v>158</v>
       </c>
-      <c r="C56" s="72" t="s">
+      <c r="C56" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="D56" s="72" t="s">
+      <c r="D56" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="E56" s="73">
+      <c r="E56" s="68">
         <v>46121</v>
       </c>
-      <c r="F56" s="73">
+      <c r="F56" s="68">
         <v>46121</v>
       </c>
-      <c r="G56" s="73">
+      <c r="G56" s="68">
         <v>46126</v>
       </c>
-      <c r="H56" s="73">
+      <c r="H56" s="68">
         <v>46126</v>
       </c>
-      <c r="I56" s="74">
+      <c r="I56" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B57" s="94" t="s">
+      <c r="B57" s="89" t="s">
         <v>160</v>
       </c>
-      <c r="C57" s="72" t="s">
+      <c r="C57" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D57" s="72" t="s">
+      <c r="D57" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="E57" s="73">
+      <c r="E57" s="68">
         <v>46127</v>
       </c>
-      <c r="F57" s="73">
+      <c r="F57" s="68">
         <v>46127</v>
       </c>
-      <c r="G57" s="73">
+      <c r="G57" s="68">
         <v>46137</v>
       </c>
-      <c r="H57" s="73">
+      <c r="H57" s="68">
         <v>46137</v>
       </c>
-      <c r="I57" s="74">
+      <c r="I57" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B58" s="94" t="s">
+      <c r="B58" s="89" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="72" t="s">
+      <c r="C58" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="D58" s="72" t="s">
+      <c r="D58" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="E58" s="73">
+      <c r="E58" s="68">
         <v>46135</v>
       </c>
-      <c r="F58" s="73">
+      <c r="F58" s="68">
         <v>46135</v>
       </c>
-      <c r="G58" s="73">
+      <c r="G58" s="68">
         <v>46138</v>
       </c>
-      <c r="H58" s="73">
+      <c r="H58" s="68">
         <v>46138</v>
       </c>
-      <c r="I58" s="74">
+      <c r="I58" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B59" s="94" t="s">
+      <c r="B59" s="89" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="72" t="s">
+      <c r="C59" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="D59" s="72" t="s">
+      <c r="D59" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="E59" s="73">
+      <c r="E59" s="68">
         <v>46130</v>
       </c>
-      <c r="F59" s="73">
+      <c r="F59" s="68">
         <v>46135</v>
       </c>
-      <c r="G59" s="73">
+      <c r="G59" s="68">
         <v>46138</v>
       </c>
-      <c r="H59" s="73">
+      <c r="H59" s="68">
         <v>46138</v>
       </c>
-      <c r="I59" s="74">
+      <c r="I59" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="C60" s="72" t="s">
+      <c r="C60" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="D60" s="72" t="s">
+      <c r="D60" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="E60" s="73">
+      <c r="E60" s="68">
         <v>46135</v>
       </c>
-      <c r="F60" s="73">
+      <c r="F60" s="68">
         <v>46135</v>
       </c>
-      <c r="G60" s="73">
+      <c r="G60" s="68">
         <v>46138</v>
       </c>
-      <c r="H60" s="73">
+      <c r="H60" s="68">
         <v>46138</v>
       </c>
-      <c r="I60" s="74">
+      <c r="I60" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B61" s="94" t="s">
+      <c r="B61" s="89" t="s">
         <v>168</v>
       </c>
-      <c r="C61" s="72" t="s">
+      <c r="C61" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="D61" s="72" t="s">
+      <c r="D61" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="E61" s="73">
+      <c r="E61" s="68">
         <v>46139</v>
       </c>
-      <c r="F61" s="73">
+      <c r="F61" s="68">
         <v>46139</v>
       </c>
-      <c r="G61" s="73">
+      <c r="G61" s="68">
         <v>46143</v>
       </c>
-      <c r="H61" s="73">
+      <c r="H61" s="68">
         <v>46143</v>
       </c>
-      <c r="I61" s="74">
+      <c r="I61" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B62" s="94" t="s">
+      <c r="B62" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="C62" s="72" t="s">
+      <c r="C62" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="72" t="s">
+      <c r="D62" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="E62" s="73">
+      <c r="E62" s="68">
         <v>46144</v>
       </c>
-      <c r="F62" s="73">
+      <c r="F62" s="68">
         <v>46144</v>
       </c>
-      <c r="G62" s="73">
+      <c r="G62" s="68">
         <v>46147</v>
       </c>
-      <c r="H62" s="73">
+      <c r="H62" s="68">
         <v>46147</v>
       </c>
-      <c r="I62" s="74">
+      <c r="I62" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B63" s="94" t="s">
+      <c r="B63" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="C63" s="72" t="s">
+      <c r="C63" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="D63" s="72" t="s">
+      <c r="D63" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="73">
+      <c r="E63" s="68">
         <v>46148</v>
       </c>
-      <c r="F63" s="73">
+      <c r="F63" s="68">
         <v>46148</v>
       </c>
-      <c r="G63" s="73">
+      <c r="G63" s="68">
         <v>46157</v>
       </c>
-      <c r="H63" s="73">
+      <c r="H63" s="68">
         <v>46157</v>
       </c>
-      <c r="I63" s="74">
+      <c r="I63" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B64" s="94" t="s">
+      <c r="B64" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="C64" s="72" t="s">
+      <c r="C64" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="D64" s="72" t="s">
+      <c r="D64" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="73">
+      <c r="E64" s="68">
         <v>46160</v>
       </c>
-      <c r="F64" s="73">
+      <c r="F64" s="68">
         <v>46160</v>
       </c>
-      <c r="G64" s="73">
+      <c r="G64" s="68">
         <v>46164</v>
       </c>
-      <c r="H64" s="73">
+      <c r="H64" s="68">
         <v>46164</v>
       </c>
-      <c r="I64" s="74">
+      <c r="I64" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B65" s="94" t="s">
+      <c r="B65" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="72" t="s">
+      <c r="C65" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="D65" s="72" t="s">
+      <c r="D65" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="73">
+      <c r="E65" s="68">
         <v>46165</v>
       </c>
-      <c r="F65" s="73">
+      <c r="F65" s="68">
         <v>46165</v>
       </c>
-      <c r="G65" s="73">
+      <c r="G65" s="68">
         <v>46173</v>
       </c>
-      <c r="H65" s="73">
+      <c r="H65" s="68">
         <v>46173</v>
       </c>
-      <c r="I65" s="74">
+      <c r="I65" s="69">
         <v>1</v>
       </c>
     </row>
@@ -4139,263 +4119,263 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="71" t="s">
+      <c r="D3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="71" t="s">
+      <c r="I3" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="66" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="68">
         <v>46071</v>
       </c>
-      <c r="E4" s="73">
+      <c r="E4" s="68">
         <v>46077</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="67">
         <v>7</v>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="67">
         <v>20</v>
       </c>
-      <c r="H4" s="74">
-        <v>1</v>
-      </c>
-      <c r="I4" s="72" t="s">
+      <c r="H4" s="69">
+        <v>1</v>
+      </c>
+      <c r="I4" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="72" t="s">
+      <c r="J4" s="67" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="68">
         <v>46082</v>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="68">
         <v>46087</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="67">
         <v>6</v>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="67">
         <v>18</v>
       </c>
-      <c r="H5" s="74">
-        <v>1</v>
-      </c>
-      <c r="I5" s="72" t="s">
+      <c r="H5" s="69">
+        <v>1</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="67" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="68">
         <v>46095</v>
       </c>
-      <c r="E6" s="73">
+      <c r="E6" s="68">
         <v>46101</v>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="67">
         <v>7</v>
       </c>
-      <c r="G6" s="72">
+      <c r="G6" s="67">
         <v>25</v>
       </c>
-      <c r="H6" s="74">
-        <v>1</v>
-      </c>
-      <c r="I6" s="72" t="s">
+      <c r="H6" s="69">
+        <v>1</v>
+      </c>
+      <c r="I6" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="72" t="s">
+      <c r="J6" s="67" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="68">
         <v>46099</v>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="68">
         <v>46107</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="67">
         <v>9</v>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="67">
         <v>30</v>
       </c>
-      <c r="H7" s="74">
-        <v>1</v>
-      </c>
-      <c r="I7" s="72" t="s">
+      <c r="H7" s="69">
+        <v>1</v>
+      </c>
+      <c r="I7" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="J7" s="72" t="s">
+      <c r="J7" s="67" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="68">
         <v>46099</v>
       </c>
-      <c r="E8" s="73">
+      <c r="E8" s="68">
         <v>46107</v>
       </c>
-      <c r="F8" s="72">
+      <c r="F8" s="67">
         <v>9</v>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="67">
         <v>30</v>
       </c>
-      <c r="H8" s="74">
-        <v>1</v>
-      </c>
-      <c r="I8" s="72" t="s">
+      <c r="H8" s="69">
+        <v>1</v>
+      </c>
+      <c r="I8" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="72" t="s">
+      <c r="J8" s="67" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="68">
         <v>46120</v>
       </c>
-      <c r="E9" s="73">
+      <c r="E9" s="68">
         <v>46130</v>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="67">
         <v>11</v>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="67">
         <v>20</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="69">
         <v>0.8</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="72" t="s">
+      <c r="J9" s="67" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="68">
         <v>46147</v>
       </c>
-      <c r="E10" s="73">
+      <c r="E10" s="68">
         <v>46163</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="67">
         <v>17</v>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="67">
         <v>40</v>
       </c>
-      <c r="H10" s="74">
+      <c r="H10" s="69">
         <v>0.6</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="72" t="s">
+      <c r="J10" s="67" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="68">
         <v>46165</v>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="68">
         <v>46172</v>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="67">
         <v>9</v>
       </c>
-      <c r="G11" s="72">
+      <c r="G11" s="67">
         <v>15</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="69">
         <v>0</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="72" t="s">
+      <c r="J11" s="67" t="s">
         <v>116</v>
       </c>
     </row>
